--- a/database/databases/Standards_Calc_Database.xlsx
+++ b/database/databases/Standards_Calc_Database.xlsx
@@ -413,17 +413,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -614,9 +614,10 @@
           <t>default</t>
         </is>
       </c>
-      <c r="F5">
-        <f>ROUNDUP(protected_area / spacing_area, 0)</f>
-        <v/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FORMULA: ROUNDUP(protected_area / spacing_area, 0)</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -695,9 +696,10 @@
           <t>default</t>
         </is>
       </c>
-      <c r="F7">
-        <f>risers * storeys * floor_to_floor_height</f>
-        <v/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FORMULA: risers * storeys * floor_to_floor_height</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -736,9 +738,10 @@
           <t>default</t>
         </is>
       </c>
-      <c r="F8">
-        <f>protected_area / SQRT(spacing_area)</f>
-        <v/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FORMULA: protected_area / SQRT(spacing_area)</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -817,9 +820,10 @@
           <t>default</t>
         </is>
       </c>
-      <c r="F10">
-        <f>storeys * MAX(1, ROUNDUP(area_per_storey / effective_area_per_reel, 0))</f>
-        <v/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FORMULA: storeys * MAX(1, ROUNDUP(area_per_storey / effective_area_per_reel, 0))</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -858,9 +862,10 @@
           <t>default</t>
         </is>
       </c>
-      <c r="F11">
-        <f>hose_reel_count</f>
-        <v/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FORMULA: hose_reel_count</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1019,9 +1024,10 @@
           <t>default</t>
         </is>
       </c>
-      <c r="F15">
-        <f>ROUNDUP(protected_area / coverage_area, 0)</f>
-        <v/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FORMULA: ROUNDUP(protected_area / coverage_area, 0)</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1060,9 +1066,10 @@
           <t>default</t>
         </is>
       </c>
-      <c r="F16">
-        <f>IF(detection_selected, 1, 0)</f>
-        <v/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FORMULA: IF(detection_selected, 1, 0)</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1101,9 +1108,10 @@
           <t>default</t>
         </is>
       </c>
-      <c r="F17">
-        <f>storeys * MAX(1, exits_per_storey)</f>
-        <v/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>FORMULA: storeys * MAX(1, exits_per_storey)</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1129,7 +1137,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>max_area_class_a_no_suppression</t>
+          <t>quantity_formula</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1142,17 +1150,19 @@
           <t>default</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>675</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FORMULA: storeys * ROUNDUP((floor_area / storeys) / max_area, 0)</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>m2/extinguisher</t>
+          <t>formula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>AS2444 Table 4.1</t>
+          <t>AS2444 area basis applied floor-by-floor, using the max area for the selected (hazard, rating, suppression) combination</t>
         </is>
       </c>
     </row>
@@ -1169,30 +1179,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>max_area_class_a_fixed_suppression</t>
+          <t>min_rating_class_a</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_class</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1000</v>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>m2/extinguisher</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>AS2444 Table 4.1</t>
+          <t>AS2444 Table 4.1 - minimum acceptable rating</t>
         </is>
       </c>
     </row>
@@ -1209,31 +1221,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>class_a_quantity_formula</t>
+          <t>min_rating_class_a</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_class</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="F20">
-        <f>storeys * ROUNDUP(floor_area / max_area_class_a, 0)</f>
-        <v/>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>AS2444 Table 4.1 area basis applied floor-by-floor</t>
+          <t>AS2444 Table 4.1 - minimum acceptable rating</t>
         </is>
       </c>
     </row>
@@ -1250,30 +1263,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>max_area_class_b</t>
+          <t>min_rating_class_a</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Class B | Light | No fixed suppression</t>
+          <t>hazard_class</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Class B | Light | No fixed suppression</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>80</v>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>m2/extinguisher</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>AS2444 Table 4.2</t>
+          <t>AS2444 Table 4.1 - minimum acceptable rating</t>
         </is>
       </c>
     </row>
@@ -1290,30 +1305,30 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>max_area_class_b</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Class B | Light | Fixed suppression</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Class B | Light | Fixed suppression</t>
+          <t>Light|1A</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>m2/extinguisher</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>AS2444 Table 4.3</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
@@ -1330,30 +1345,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>max_area_class_b</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Class B | Ordinary | No fixed suppression</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Class B | Ordinary | No fixed suppression</t>
+          <t>Light|2A</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>m2/extinguisher</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>AS2444 Table 4.2</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
@@ -1370,30 +1385,30 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>max_area_class_b</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Class B | Ordinary | Fixed suppression</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Class B | Ordinary | Fixed suppression</t>
+          <t>Light|3A</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>m2/extinguisher</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>AS2444 Table 4.3</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
@@ -1410,30 +1425,30 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>max_area_class_b</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Class B | High | No fixed suppression</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Class B | High | No fixed suppression</t>
+          <t>Light|4A</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>300</v>
+        <v>675</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>m2/extinguisher</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>AS2444 Table 4.2</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
@@ -1450,30 +1465,30 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>max_area_class_b</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Class B | High | Fixed suppression</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Class B | High | Fixed suppression</t>
+          <t>Ordinary|2A</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>m2/extinguisher</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>AS2444 Table 4.3</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
@@ -1490,756 +1505,2786 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>class_b_quantity_formula</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="F27">
-        <f>ROUNDUP(risk_area / max_area_class_b, 0)</f>
-        <v/>
+          <t>Ordinary|3A</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>300</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>AS2444 Table 4.2/4.3 area basis - NOT YET WIRED into UI (needs Hazard + Fixed Suppression inputs)</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hydrant</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>hydrant_riser</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>min_risers</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>Ordinary|4A</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>450</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>no.</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Minimum riser allowance</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hydrant</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hydrant_outlet</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>outlets_per_riser_per_storey</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>Ordinary|6A</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>675</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>no/riser/storey</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PROXY - simplified AS2419.1 proxy, not a direct AS quantity rule</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hydrant</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hydrant_outlet</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>quantity_formula</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="F30">
-        <f>risers * storeys * outlets_per_riser_per_storey</f>
-        <v/>
+          <t>High|2A</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>150</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Riser-per-storey method - PROXY, verify against AS2419.1 layout</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hydrant</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>booster</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>booster_count</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>High|3A</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>no.</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Typical hydrant allowance if selected</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>emergency_lighting</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>emergency_luminaire</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>effective_area_per_luminaire</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>High|4A</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>m2/luminaire</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Density proxy - AS/NZS2293.1 is photometric-based, not m2/luminaire based</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>emergency_lighting</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>emergency_luminaire</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>quantity_formula</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="F33">
-        <f>storeys * MAX(1, ROUNDUP((protected_area / storeys) / effective_area_per_luminaire, 0))</f>
-        <v/>
+          <t>High|6A</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>450</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Area-based proxy</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>emergency_lighting</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>stair_luminaire</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>luminaires_per_stair_per_storey</t>
+          <t>max_area_class_a_no_suppression</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>High|10A</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>675</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>no/stair/storey</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Simplified stair allowance</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>emergency_lighting</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>stair_luminaire</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>quantity_formula</t>
+          <t>max_area_class_a_with_suppression</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="F35">
-        <f>stairs * storeys * luminaires_per_stair_per_storey</f>
-        <v/>
+          <t>Light|1A</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>150</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Stair lighting allowance</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>emergency_lighting</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>emergency_luminaire</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>egress_corridor_factor</t>
+          <t>max_area_class_a_with_suppression</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>Light|2A</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>450</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>multiplier</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Default egress corridor allowance - user override recommended</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>exit_signs</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>exit_sign</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>signs_per_exit</t>
+          <t>max_area_class_a_with_suppression</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>Light|3A</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>675</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>no/exit</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Simplified allowance</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>exit_signs</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>exit_sign</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>quantity_formula</t>
+          <t>max_area_class_a_with_suppression</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="F38">
-        <f>storeys * exits_per_storey * signs_per_exit</f>
-        <v/>
+          <t>Light|4A</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Required-exit based estimate</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>exit_signs</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>directional_sign</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>area_allowance</t>
+          <t>max_area_class_a_with_suppression</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>Ordinary|2A</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>m2/sign</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PROXY - wayfinding proxy where path layout is unavailable</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>exit_signs</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>directional_sign</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>quantity_formula</t>
+          <t>max_area_class_a_with_suppression</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="F40">
-        <f>storeys * ROUNDUP((protected_area / storeys) / area_allowance, 0)</f>
-        <v/>
+          <t>Ordinary|3A</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>450</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Area-based proxy - low confidence</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>alarm_warning</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>sounder</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>coverage_area</t>
+          <t>max_area_class_a_with_suppression</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>Ordinary|4A</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>250</v>
+        <v>675</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>m2/device</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>PROXY - AS1670.4 is performance-based, no simple m2/device estimator exists</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>alarm_warning</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>speaker</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>coverage_area</t>
+          <t>max_area_class_a_with_suppression</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>Ordinary|6A</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>m2/device</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PROXY - actual quantity depends on acoustic design</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>alarm_warning</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>strobe</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>coverage_area</t>
+          <t>max_area_class_a_with_suppression</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>High|2A</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>m2/device</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PROXY - actual requirement depends on occupancy/accessibility</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>alarm_warning</t>
+          <t>extinguisher</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>warning_device</t>
+          <t>portable_extinguisher</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>quantity_formula</t>
+          <t>max_area_class_a_with_suppression</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>hazard_rating</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="F44">
-        <f>ROUNDUP(protected_area / coverage_area, 0)</f>
-        <v/>
+          <t>High|3A</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>300</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Area-based proxy - low confidence, verify against AS1670.4</t>
+          <t>AS2444 Table 4.1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>max_area_class_a_with_suppression</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>High|4A</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>450</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>max_area_class_a_with_suppression</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>High|6A</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>675</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>max_area_class_a_with_suppression</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>High|10A</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>min_rating_class_b</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>hazard_class</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2 - minimum acceptable rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>min_rating_class_b</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>hazard_class</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>20B</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2 - minimum acceptable rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>min_rating_class_b</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>hazard_class</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>40B</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2 - minimum acceptable rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>max_area_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Light|5B</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>15</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>max_area_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Light|10B</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>45</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>max_area_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Light|20B</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>80</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>max_area_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ordinary|20B</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>80</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>max_area_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ordinary|30B</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>115</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>max_area_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ordinary|40B</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>150</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>max_area_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>High|40B</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>150</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>max_area_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>High|60B</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>225</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>max_area_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>High|80B</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>300</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>max_area_class_b_with_suppression</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Light|5B</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>80</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>max_area_class_b_with_suppression</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Light|10B</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>115</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>max_area_class_b_with_suppression</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Light|20B</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>150</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>max_area_class_b_with_suppression</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ordinary|20B</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>150</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>max_area_class_b_with_suppression</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Ordinary|30B</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>225</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>max_area_class_b_with_suppression</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ordinary|40B</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>300</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>max_area_class_b_with_suppression</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>High|40B</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>150</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>max_area_class_b_with_suppression</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>High|60B</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>225</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>max_area_class_b_with_suppression</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>High|80B</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>300</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>travel_distance_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Light|5B</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2 to 3</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>travel_distance_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Light|10B</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2 to 4</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>travel_distance_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Light|20B</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2 to 5</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>travel_distance_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Ordinary|20B</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>3 to 5</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>travel_distance_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ordinary|30B</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>3 to 7.5</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>travel_distance_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Ordinary|40B</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>3 to 10</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>travel_distance_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>High|40B</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>4 to 10</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>travel_distance_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>High|60B</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>4 to 12.5</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>extinguisher</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>portable_extinguisher</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>travel_distance_class_b_no_suppression</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>hazard_rating</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>High|80B</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>4 to 15</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>AS2444 Table 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>hydrant</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>hydrant_riser</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>min_risers</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>no.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Minimum riser allowance</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>hydrant</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>hydrant_outlet</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>outlets_per_riser_per_storey</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>no/riser/storey</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>PROXY - simplified AS2419.1 proxy, not a direct AS quantity rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>hydrant</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>hydrant_outlet</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>quantity_formula</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>FORMULA: risers * storeys * outlets_per_riser_per_storey</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Riser-per-storey method - PROXY, verify against AS2419.1 layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>hydrant</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>booster</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>booster_count</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>no.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Typical hydrant allowance if selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>emergency_lighting</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>emergency_luminaire</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>effective_area_per_luminaire</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>100</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>m2/luminaire</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Density proxy - AS/NZS2293.1 is photometric-based, not m2/luminaire based</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>emergency_lighting</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>emergency_luminaire</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>quantity_formula</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>FORMULA: storeys * MAX(1, ROUNDUP((protected_area / storeys) / effective_area_per_luminaire, 0))</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Area-based proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>emergency_lighting</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>stair_luminaire</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>luminaires_per_stair_per_storey</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>no/stair/storey</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Simplified stair allowance</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>emergency_lighting</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>stair_luminaire</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>quantity_formula</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>FORMULA: stairs * storeys * luminaires_per_stair_per_storey</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Stair lighting allowance</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>emergency_lighting</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>emergency_luminaire</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>egress_corridor_factor</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>10</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>multiplier</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Default egress corridor allowance - user override recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>exit_signs</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>exit_sign</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>signs_per_exit</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>no/exit</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Simplified allowance</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>exit_signs</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>exit_sign</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>quantity_formula</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>FORMULA: storeys * exits_per_storey * signs_per_exit</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Required-exit based estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>exit_signs</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>directional_sign</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>area_allowance</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>500</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>m2/sign</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>PROXY - wayfinding proxy where path layout is unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>exit_signs</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>directional_sign</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>quantity_formula</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>FORMULA: storeys * ROUNDUP((protected_area / storeys) / area_allowance, 0)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Area-based proxy - low confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>alarm_warning</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>sounder</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>coverage_area</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>250</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>m2/device</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>PROXY - AS1670.4 is performance-based, no simple m2/device estimator exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>alarm_warning</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>speaker</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>coverage_area</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>200</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>m2/device</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>PROXY - actual quantity depends on acoustic design</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>alarm_warning</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>strobe</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>coverage_area</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>250</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>m2/device</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>PROXY - actual requirement depends on occupancy/accessibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>alarm_warning</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>warning_device</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>quantity_formula</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>FORMULA: ROUNDUP(protected_area / coverage_area, 0)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Area-based proxy - low confidence, verify against AS1670.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>alarm_warning</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>control_panel</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>count_formula</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="F45">
-        <f>IF(alarm_warning_selected, 1, 0)</f>
-        <v/>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>FORMULA: IF(alarm_warning_selected, 1, 0)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>One panel per system</t>
         </is>
